--- a/in-PRS.xlsx
+++ b/in-PRS.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20338"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5755FF6-254C-4176-840D-AC25DD87F8F7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A88AE8-0651-451F-93BB-544BB7CBA052}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8390" activeTab="3" xr2:uid="{6F95609E-9E9F-404E-AAE5-32499E75A13B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8390" activeTab="1" xr2:uid="{6F95609E-9E9F-404E-AAE5-32499E75A13B}"/>
   </bookViews>
   <sheets>
     <sheet name="Level" sheetId="18" r:id="rId1"/>
@@ -1267,7 +1267,7 @@
         <v>95</v>
       </c>
       <c r="D17" s="26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E17" s="10">
         <v>3</v>
@@ -1284,7 +1284,7 @@
         <v>95</v>
       </c>
       <c r="D18" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E18" s="10">
         <v>2</v>
@@ -1301,7 +1301,7 @@
         <v>95</v>
       </c>
       <c r="D19" s="26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E19" s="10">
         <v>35</v>
@@ -1318,7 +1318,7 @@
         <v>95</v>
       </c>
       <c r="D20" s="26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E20" s="10">
         <v>8</v>
@@ -1335,7 +1335,7 @@
         <v>95</v>
       </c>
       <c r="D21" s="26">
-        <v>7.25</v>
+        <v>0.75</v>
       </c>
       <c r="E21" s="10">
         <v>54</v>
@@ -1352,7 +1352,7 @@
         <v>95</v>
       </c>
       <c r="D22" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E22" s="10">
         <v>1</v>
@@ -1369,7 +1369,7 @@
         <v>95</v>
       </c>
       <c r="D23" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E23" s="10">
         <v>13</v>
@@ -1386,7 +1386,7 @@
         <v>95</v>
       </c>
       <c r="D24" s="26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" s="6">
         <v>10</v>
@@ -1403,7 +1403,7 @@
         <v>95</v>
       </c>
       <c r="D25" s="26">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="E25" s="6">
         <v>4</v>
@@ -1437,7 +1437,7 @@
         <v>95</v>
       </c>
       <c r="D27" s="26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E27" s="6">
         <v>62</v>
@@ -1454,7 +1454,7 @@
         <v>95</v>
       </c>
       <c r="D28" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" s="6">
         <v>18</v>
@@ -1471,7 +1471,7 @@
         <v>95</v>
       </c>
       <c r="D29" s="26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" s="6">
         <v>26</v>
@@ -1488,7 +1488,7 @@
         <v>95</v>
       </c>
       <c r="D30" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E30" s="6">
         <v>15</v>
@@ -1505,7 +1505,7 @@
         <v>95</v>
       </c>
       <c r="D31" s="26">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="E31" s="6">
         <v>54</v>
@@ -1522,7 +1522,7 @@
         <v>95</v>
       </c>
       <c r="D32" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E32" s="6">
         <v>31</v>
@@ -1539,7 +1539,7 @@
         <v>95</v>
       </c>
       <c r="D33" s="26">
-        <v>7.25</v>
+        <v>0.75</v>
       </c>
       <c r="E33" s="6">
         <v>24</v>
@@ -1556,7 +1556,7 @@
         <v>95</v>
       </c>
       <c r="D34" s="26">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="E34" s="6">
         <v>51</v>
@@ -1573,7 +1573,7 @@
         <v>95</v>
       </c>
       <c r="D35" s="26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E35" s="6">
         <v>60</v>
@@ -1590,7 +1590,7 @@
         <v>95</v>
       </c>
       <c r="D36" s="26">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="E36" s="6">
         <v>18</v>
@@ -1624,7 +1624,7 @@
         <v>95</v>
       </c>
       <c r="D38" s="26">
-        <v>7.25</v>
+        <v>0.75</v>
       </c>
       <c r="E38" s="6">
         <v>44</v>
@@ -1641,7 +1641,7 @@
         <v>95</v>
       </c>
       <c r="D39" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E39" s="6">
         <v>200</v>
@@ -1675,7 +1675,7 @@
         <v>95</v>
       </c>
       <c r="D41" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E41" s="6">
         <v>52</v>
@@ -1692,7 +1692,7 @@
         <v>95</v>
       </c>
       <c r="D42" s="26">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="E42" s="6">
         <v>21</v>
@@ -1709,7 +1709,7 @@
         <v>95</v>
       </c>
       <c r="D43" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E43" s="6">
         <v>61</v>
@@ -1726,7 +1726,7 @@
         <v>95</v>
       </c>
       <c r="D44" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" s="6">
         <v>13</v>
@@ -1743,7 +1743,7 @@
         <v>95</v>
       </c>
       <c r="D45" s="26">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E45" s="6">
         <v>16</v>
@@ -1777,7 +1777,7 @@
         <v>95</v>
       </c>
       <c r="D47" s="26">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="E47" s="6">
         <v>119</v>
@@ -1794,7 +1794,7 @@
         <v>95</v>
       </c>
       <c r="D48" s="26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" s="6">
         <v>91</v>
@@ -1811,7 +1811,7 @@
         <v>95</v>
       </c>
       <c r="D49" s="26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="E49" s="6">
         <v>281</v>
@@ -1828,7 +1828,7 @@
         <v>95</v>
       </c>
       <c r="D50" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E50" s="6">
         <v>91</v>
@@ -1845,7 +1845,7 @@
         <v>95</v>
       </c>
       <c r="D51" s="26">
-        <v>5.75</v>
+        <v>2.25</v>
       </c>
       <c r="E51" s="6">
         <v>31</v>
@@ -1862,7 +1862,7 @@
         <v>95</v>
       </c>
       <c r="D52" s="26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E52" s="6">
         <v>6</v>
@@ -1879,7 +1879,7 @@
         <v>95</v>
       </c>
       <c r="D53" s="26">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E53" s="6">
         <v>11</v>
@@ -1896,7 +1896,7 @@
         <v>95</v>
       </c>
       <c r="D54" s="26">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="E54" s="6">
         <v>39</v>
@@ -1913,7 +1913,7 @@
         <v>95</v>
       </c>
       <c r="D55" s="26">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E55" s="6">
         <v>3</v>
@@ -1934,7 +1934,7 @@
     <col min="1" max="16384" width="8.6640625" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>137</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>65</v>
       </c>
@@ -2160,7 +2160,7 @@
       <c r="BB2" s="10"/>
       <c r="BC2" s="10"/>
     </row>
-    <row r="3" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>62</v>
       </c>
@@ -2223,7 +2223,7 @@
       <c r="BB3" s="10"/>
       <c r="BC3" s="22"/>
     </row>
-    <row r="4" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>63</v>
       </c>
@@ -2286,7 +2286,7 @@
       <c r="BB4" s="10"/>
       <c r="BC4" s="22"/>
     </row>
-    <row r="5" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>64</v>
       </c>
@@ -2347,7 +2347,7 @@
       <c r="BB5" s="10"/>
       <c r="BC5" s="22"/>
     </row>
-    <row r="6" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>61</v>
       </c>
@@ -2414,7 +2414,7 @@
       <c r="BB6" s="10"/>
       <c r="BC6" s="10"/>
     </row>
-    <row r="7" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>66</v>
       </c>
@@ -2479,7 +2479,7 @@
       <c r="BB7" s="10"/>
       <c r="BC7" s="10"/>
     </row>
-    <row r="8" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>67</v>
       </c>
@@ -2540,7 +2540,7 @@
       <c r="BB8" s="10"/>
       <c r="BC8" s="10"/>
     </row>
-    <row r="9" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>68</v>
       </c>
@@ -2607,7 +2607,7 @@
       <c r="BB9" s="10"/>
       <c r="BC9" s="10"/>
     </row>
-    <row r="10" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>69</v>
       </c>
@@ -2670,7 +2670,7 @@
       <c r="BB10" s="10"/>
       <c r="BC10" s="10"/>
     </row>
-    <row r="11" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>70</v>
       </c>
@@ -2731,7 +2731,7 @@
       <c r="BB11" s="10"/>
       <c r="BC11" s="10"/>
     </row>
-    <row r="12" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
         <v>71</v>
       </c>
@@ -2794,7 +2794,7 @@
       <c r="BB12" s="10"/>
       <c r="BC12" s="10"/>
     </row>
-    <row r="13" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
         <v>72</v>
       </c>
@@ -2861,7 +2861,7 @@
       <c r="BB13" s="10"/>
       <c r="BC13" s="10"/>
     </row>
-    <row r="14" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
         <v>73</v>
       </c>
@@ -2922,7 +2922,7 @@
       <c r="BB14" s="10"/>
       <c r="BC14" s="10"/>
     </row>
-    <row r="15" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>74</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="BB15" s="10"/>
       <c r="BC15" s="10"/>
     </row>
-    <row r="16" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>75</v>
       </c>
@@ -3050,7 +3050,7 @@
       <c r="BB16" s="10"/>
       <c r="BC16" s="10"/>
     </row>
-    <row r="17" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
@@ -3121,7 +3121,7 @@
       <c r="BB17" s="23"/>
       <c r="BC17" s="23"/>
     </row>
-    <row r="18" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>23</v>
       </c>
@@ -3190,7 +3190,7 @@
       <c r="BB18" s="23"/>
       <c r="BC18" s="23"/>
     </row>
-    <row r="19" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>24</v>
       </c>
@@ -3253,7 +3253,7 @@
       <c r="BB19" s="23"/>
       <c r="BC19" s="23"/>
     </row>
-    <row r="20" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
@@ -3326,7 +3326,7 @@
       <c r="BB20" s="23"/>
       <c r="BC20" s="23"/>
     </row>
-    <row r="21" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
         <v>26</v>
       </c>
@@ -3389,7 +3389,7 @@
       <c r="BB21" s="23"/>
       <c r="BC21" s="23"/>
     </row>
-    <row r="22" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
         <v>27</v>
       </c>
@@ -3450,7 +3450,7 @@
       <c r="BB22" s="23"/>
       <c r="BC22" s="23"/>
     </row>
-    <row r="23" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
         <v>28</v>
       </c>
@@ -3515,7 +3515,7 @@
       <c r="BB23" s="23"/>
       <c r="BC23" s="23"/>
     </row>
-    <row r="24" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
         <v>29</v>
       </c>
@@ -3582,7 +3582,7 @@
       <c r="BB24" s="23"/>
       <c r="BC24" s="23"/>
     </row>
-    <row r="25" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
         <v>30</v>
       </c>
@@ -3643,7 +3643,7 @@
       <c r="BB25" s="23"/>
       <c r="BC25" s="23"/>
     </row>
-    <row r="26" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A26" s="8" t="s">
         <v>31</v>
       </c>
@@ -3704,7 +3704,7 @@
       <c r="BB26" s="23"/>
       <c r="BC26" s="23"/>
     </row>
-    <row r="27" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
         <v>32</v>
       </c>
@@ -3767,7 +3767,7 @@
       <c r="BB27" s="23"/>
       <c r="BC27" s="23"/>
     </row>
-    <row r="28" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>33</v>
       </c>
@@ -3832,7 +3832,7 @@
       <c r="BB28" s="23"/>
       <c r="BC28" s="23"/>
     </row>
-    <row r="29" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>34</v>
       </c>
@@ -3899,7 +3899,7 @@
       <c r="BB29" s="23"/>
       <c r="BC29" s="23"/>
     </row>
-    <row r="30" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>35</v>
       </c>
@@ -3960,7 +3960,7 @@
       <c r="BB30" s="23"/>
       <c r="BC30" s="23"/>
     </row>
-    <row r="31" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>36</v>
       </c>
@@ -4023,7 +4023,7 @@
       <c r="BB31" s="23"/>
       <c r="BC31" s="23"/>
     </row>
-    <row r="32" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>37</v>
       </c>
@@ -4084,7 +4084,7 @@
       <c r="BB32" s="23"/>
       <c r="BC32" s="23"/>
     </row>
-    <row r="33" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>38</v>
       </c>
@@ -4149,7 +4149,7 @@
       <c r="BB33" s="23"/>
       <c r="BC33" s="23"/>
     </row>
-    <row r="34" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>39</v>
       </c>
@@ -4210,7 +4210,7 @@
       <c r="BB34" s="23"/>
       <c r="BC34" s="23"/>
     </row>
-    <row r="35" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>40</v>
       </c>
@@ -4271,7 +4271,7 @@
       <c r="BB35" s="23"/>
       <c r="BC35" s="23"/>
     </row>
-    <row r="36" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
         <v>41</v>
       </c>
@@ -4332,7 +4332,7 @@
       <c r="BB36" s="23"/>
       <c r="BC36" s="23"/>
     </row>
-    <row r="37" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A37" s="8" t="s">
         <v>42</v>
       </c>
@@ -4397,7 +4397,7 @@
       <c r="BB37" s="23"/>
       <c r="BC37" s="23"/>
     </row>
-    <row r="38" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
         <v>43</v>
       </c>
@@ -4470,7 +4470,7 @@
       <c r="BB38" s="23"/>
       <c r="BC38" s="23"/>
     </row>
-    <row r="39" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
         <v>44</v>
       </c>
@@ -4535,7 +4535,7 @@
       <c r="BB39" s="23"/>
       <c r="BC39" s="23"/>
     </row>
-    <row r="40" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
         <v>45</v>
       </c>
@@ -4596,7 +4596,7 @@
       <c r="BB40" s="23"/>
       <c r="BC40" s="23"/>
     </row>
-    <row r="41" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
         <v>46</v>
       </c>
@@ -4659,7 +4659,7 @@
       <c r="BB41" s="23"/>
       <c r="BC41" s="23"/>
     </row>
-    <row r="42" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>47</v>
       </c>
@@ -4724,7 +4724,7 @@
       <c r="BB42" s="23"/>
       <c r="BC42" s="23"/>
     </row>
-    <row r="43" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>48</v>
       </c>
@@ -4787,7 +4787,7 @@
       <c r="BB43" s="23"/>
       <c r="BC43" s="23"/>
     </row>
-    <row r="44" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>49</v>
       </c>
@@ -4858,7 +4858,7 @@
       <c r="BB44" s="23"/>
       <c r="BC44" s="23"/>
     </row>
-    <row r="45" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>50</v>
       </c>
@@ -4923,7 +4923,7 @@
       <c r="BB45" s="23"/>
       <c r="BC45" s="23"/>
     </row>
-    <row r="46" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>51</v>
       </c>
@@ -4984,7 +4984,7 @@
       <c r="BB46" s="23"/>
       <c r="BC46" s="23"/>
     </row>
-    <row r="47" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>52</v>
       </c>
@@ -5049,7 +5049,7 @@
       <c r="BB47" s="23"/>
       <c r="BC47" s="23"/>
     </row>
-    <row r="48" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
         <v>53</v>
       </c>
@@ -5112,7 +5112,7 @@
       <c r="BB48" s="23"/>
       <c r="BC48" s="23"/>
     </row>
-    <row r="49" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
         <v>54</v>
       </c>
@@ -5175,7 +5175,7 @@
       <c r="BB49" s="23"/>
       <c r="BC49" s="23"/>
     </row>
-    <row r="50" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>55</v>
       </c>
@@ -5238,7 +5238,7 @@
       <c r="BB50" s="23"/>
       <c r="BC50" s="23"/>
     </row>
-    <row r="51" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>56</v>
       </c>
@@ -5303,7 +5303,7 @@
       <c r="BB51" s="23"/>
       <c r="BC51" s="23"/>
     </row>
-    <row r="52" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>57</v>
       </c>
@@ -5368,7 +5368,7 @@
       <c r="BB52" s="23"/>
       <c r="BC52" s="23"/>
     </row>
-    <row r="53" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>58</v>
       </c>
@@ -5429,7 +5429,7 @@
       <c r="BB53" s="23"/>
       <c r="BC53" s="23"/>
     </row>
-    <row r="54" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>59</v>
       </c>
@@ -5490,7 +5490,7 @@
       <c r="BB54" s="23"/>
       <c r="BC54" s="23"/>
     </row>
-    <row r="55" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:55" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>60</v>
       </c>
